--- a/data/obx_xlsx/HBC.OL.xlsx
+++ b/data/obx_xlsx/HBC.OL.xlsx
@@ -9055,7 +9055,10 @@
       <c r="P34" s="15">
         <v>67.1</v>
       </c>
-      <c r="Q34" s="16"/>
+      <c r="Q34" s="16">
+        <f>SUM(Q36,Q40)</f>
+        <v>32.18</v>
+      </c>
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="13" t="s">
